--- a/data/trans_dic/P1418-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1418-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,63</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,95</t>
+          <t>0,1; 0,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,38</t>
+          <t>0,26; 2,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,01</t>
+          <t>0,34; 1,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,01</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,25</t>
+          <t>1,58; 4,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,81</t>
+          <t>0,33; 1,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,51</t>
+          <t>0,57; 2,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,41</t>
+          <t>0,39; 2,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,56</t>
+          <t>1,05; 2,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,2</t>
+          <t>0,36; 1,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,43</t>
+          <t>0,24; 1,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,35</t>
+          <t>1,05; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,72</t>
+          <t>0,13; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,37</t>
+          <t>0,36; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,39</t>
+          <t>3,98; 7,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,76</t>
+          <t>2,78; 6,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,16</t>
+          <t>1,54; 4,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,37; 4,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,79</t>
+          <t>2,77; 4,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,4</t>
+          <t>1,58; 3,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,98</t>
+          <t>0,75; 2,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,06</t>
+          <t>1,57; 3,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,52</t>
+          <t>3,41; 7,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,24</t>
+          <t>0,84; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,1</t>
+          <t>0,89; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,89</t>
+          <t>2,74; 5,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,63</t>
+          <t>7,54; 12,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,32</t>
+          <t>4,21; 8,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,65</t>
+          <t>2,44; 5,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,84</t>
+          <t>6,24; 9,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,35</t>
+          <t>5,85; 9,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,31</t>
+          <t>2,95; 5,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,76</t>
+          <t>1,93; 3,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,8</t>
+          <t>4,95; 7,17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 15,16</t>
+          <t>8,63; 15,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,25</t>
+          <t>1,89; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,95</t>
+          <t>1,57; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,07</t>
+          <t>3,47; 6,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,64</t>
+          <t>8,86; 15,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,84</t>
+          <t>10,05; 16,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 12,54</t>
+          <t>7,2; 13,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,36</t>
+          <t>8,3; 12,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,45</t>
+          <t>9,7; 14,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,28</t>
+          <t>6,63; 10,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,34</t>
+          <t>4,97; 8,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,94</t>
+          <t>6,3; 8,8</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 19,22</t>
+          <t>11,29; 19,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,57</t>
+          <t>7,06; 14,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,22</t>
+          <t>3,86; 9,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,82</t>
+          <t>5,97; 10,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,31</t>
+          <t>19,52; 28,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 25,39</t>
+          <t>16,71; 25,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,39; 20,35</t>
+          <t>12,35; 20,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 13,27</t>
+          <t>10,85; 15,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,71</t>
+          <t>16,51; 22,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,16; 18,71</t>
+          <t>13,14; 18,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,31</t>
+          <t>9,06; 14,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,16</t>
+          <t>9,0; 12,42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,34; 26,92</t>
+          <t>16,78; 27,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 22,87</t>
+          <t>12,77; 23,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,07</t>
+          <t>9,29; 17,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 18,75</t>
+          <t>12,07; 18,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 36,8</t>
+          <t>26,03; 36,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,1; 41,17</t>
+          <t>31,23; 40,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,19; 28,64</t>
+          <t>19,49; 28,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,29; 29,05</t>
+          <t>23,62; 29,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,89; 31,73</t>
+          <t>24,07; 31,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,12; 32,86</t>
+          <t>25,0; 32,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,81; 22,8</t>
+          <t>16,25; 22,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,89; 24,39</t>
+          <t>19,94; 24,31</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,28</t>
+          <t>4,76; 6,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,76</t>
+          <t>2,51; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,94</t>
+          <t>1,9; 3,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,73</t>
+          <t>3,63; 4,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,28</t>
+          <t>9,16; 11,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,8</t>
+          <t>8,8; 10,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,16</t>
+          <t>6,28; 8,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,31</t>
+          <t>8,08; 9,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,48</t>
+          <t>7,14; 8,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,08</t>
+          <t>5,91; 7,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,38</t>
+          <t>4,24; 5,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,8</t>
+          <t>6,11; 7,13</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7794</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4164</t>
+          <t>0; 4123</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,22 +2078,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5598</t>
+          <t>0; 5574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 23147</t>
+          <t>0; 20867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>899; 7634</t>
+          <t>898; 7552</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,27 +2103,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 19772</t>
+          <t>0; 17361</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>937; 9133</t>
+          <t>938; 8794</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4871</t>
+          <t>0; 4917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5226</t>
+          <t>0; 6333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1596; 24132</t>
+          <t>2038; 21252</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6265</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2586; 14782</t>
+          <t>2527; 12713</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>912; 6969</t>
+          <t>913; 7530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4730</t>
+          <t>0; 5754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5799</t>
+          <t>0; 7221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10063; 26556</t>
+          <t>9856; 27016</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1982; 11060</t>
+          <t>2032; 11627</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2972; 14159</t>
+          <t>3216; 14678</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1796; 12331</t>
+          <t>1937; 11702</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14830; 34856</t>
+          <t>14291; 35051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4049; 15554</t>
+          <t>4725; 17055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3899; 16601</t>
+          <t>3882; 16623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2427; 13393</t>
+          <t>2317; 12920</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>27691</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6608; 21393</t>
+          <t>6710; 21702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>901; 11736</t>
+          <t>896; 12763</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2499,47 +2499,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2024; 12631</t>
+          <t>2253; 13611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26385; 50999</t>
+          <t>27439; 50470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19212; 40878</t>
+          <t>19693; 42911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10141; 27481</t>
+          <t>10196; 26642</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11371; 25551</t>
+          <t>14687; 30412</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37160; 63693</t>
+          <t>36814; 64871</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22132; 47342</t>
+          <t>21974; 47329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10826; 26372</t>
+          <t>10000; 26662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16020; 32877</t>
+          <t>19507; 38197</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>85756</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17986; 39065</t>
+          <t>17682; 40470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4877; 19922</t>
+          <t>5193; 19348</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5582; 20037</t>
+          <t>5737; 20163</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11127; 43401</t>
+          <t>19201; 41498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38777; 65114</t>
+          <t>38880; 66864</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25725; 51034</t>
+          <t>25817; 49796</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15969; 36676</t>
+          <t>15847; 36455</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44857; 76946</t>
+          <t>45794; 68789</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61098; 96765</t>
+          <t>60504; 94297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35825; 65214</t>
+          <t>36239; 65925</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24689; 48742</t>
+          <t>24958; 49679</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52808; 108614</t>
+          <t>71001; 102757</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>60897</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83873</t>
+          <t>90778</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34092; 58633</t>
+          <t>33364; 58304</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8000; 22531</t>
+          <t>8101; 22623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7516; 23639</t>
+          <t>7503; 23824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20148; 39624</t>
+          <t>21096; 41381</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36961; 63163</t>
+          <t>35777; 61758</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45326; 75417</t>
+          <t>44996; 73936</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34202; 62328</t>
+          <t>35785; 64653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45157; 67277</t>
+          <t>50319; 73591</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76285; 114265</t>
+          <t>76681; 111950</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56535; 90199</t>
+          <t>58192; 90825</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47780; 81277</t>
+          <t>48423; 81324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69818; 98769</t>
+          <t>76544; 106849</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51372</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81979</t>
+          <t>89419</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32620; 56223</t>
+          <t>33042; 56208</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21434; 45144</t>
+          <t>21877; 43894</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12702; 30838</t>
+          <t>12908; 30969</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22688; 39764</t>
+          <t>24244; 42184</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66557; 97082</t>
+          <t>66931; 96488</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59381; 89888</t>
+          <t>59158; 88803</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46795; 76862</t>
+          <t>46639; 76173</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19426; 80621</t>
+          <t>47555; 67710</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>106418; 144351</t>
+          <t>104919; 143206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87330; 124213</t>
+          <t>87206; 125861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65773; 101906</t>
+          <t>64543; 99966</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43555; 108847</t>
+          <t>75995; 104890</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43241</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>111897</t>
+          <t>122479</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>155139</t>
+          <t>170786</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34286; 56503</t>
+          <t>35215; 57967</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31509; 57146</t>
+          <t>31909; 58086</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24857; 46429</t>
+          <t>23873; 44345</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34869; 53030</t>
+          <t>37442; 58647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86393; 122887</t>
+          <t>86911; 122354</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>120984; 160151</t>
+          <t>121479; 158914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76812; 114605</t>
+          <t>77998; 114419</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99028; 123511</t>
+          <t>109576; 137575</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>129895; 172557</t>
+          <t>130908; 172679</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160501; 209912</t>
+          <t>159691; 204754</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103866; 149801</t>
+          <t>106805; 149920</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>140789; 172689</t>
+          <t>154332; 188230</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>154201; 205646</t>
+          <t>156040; 206738</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>88191; 128787</t>
+          <t>86064; 129575</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64345; 99877</t>
+          <t>64449; 101690</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>109528; 163291</t>
+          <t>127983; 172386</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>308880; 381226</t>
+          <t>309379; 378888</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>309986; 383820</t>
+          <t>312931; 383193</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>223146; 289290</t>
+          <t>222423; 285859</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>251747; 340066</t>
+          <t>301096; 357002</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>482505; 564282</t>
+          <t>475182; 565293</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>413206; 494468</t>
+          <t>412841; 497025</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>301375; 373029</t>
+          <t>294386; 373711</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>379743; 483252</t>
+          <t>443396; 517126</t>
         </is>
       </c>
     </row>
